--- a/feedback_forms/042_medication_release_feedback_form--feedback_forms.xlsx
+++ b/feedback_forms/042_medication_release_feedback_form--feedback_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -878,7 +878,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>hospital_name</t>
+          <t>hospital_name_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>unit_number</t>
+          <t>unit_number_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>patient_name</t>
+          <t>patient_name_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>release_nurse_name</t>
+          <t>release_nurse_name_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>release_nurse_phone</t>
+          <t>release_nurse_phone_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Release Nurse Phone</t>
+          <t>Release Nurse Phone 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1016,12 +1016,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>patient_phone</t>
+          <t>patient_phone_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Patient Phone</t>
+          <t>Patient Phone 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>patient_email</t>
+          <t>patient_email_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>hospital_name</t>
+          <t>hospital_name_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Hospital</t>
+          <t>Hospital Name 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
